--- a/review/etnografiya/may-december/december/december.xlsx
+++ b/review/etnografiya/may-december/december/december.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему длинная шуба подходит не для всякого дела?</t>
+          <t xml:space="preserve">Полушубок оставляет больше свободы для работы, чем длинная верхняя одежда. Длина вещи связана с движением человека в зимнем хозяйстве.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как форма связана с работой на морозе?</t>
+          <t xml:space="preserve">Рукавица собирает пальцы в общем пространстве. Материал и следы износа помогают увидеть, как одежда служила рукам на морозе.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что наматывали на ногу перед выходом?</t>
+          <t xml:space="preserve">Онучи входят в обувной комплект раньше лаптя. Несколько слоёв работают вместе — повседневная обувь начинается с подготовки самой ноги.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему в народном описании появляются сани?</t>
+          <t xml:space="preserve">В народных описаниях Введения появляется зимний выезд. Сани связывают праздничную встречу с дорогой, которая стала доступна по снегу.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рабочие сани выглядят иначе, чем прогулочные?</t>
+          <t xml:space="preserve">Розвальни расширяют место для хозяйственного груза. Рабочие сани отличаются от прогулочных потому, что служат другому содержимому и делу.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -243,7 +243,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как уложить длинные поленья на короткую основу?</t>
+          <t xml:space="preserve">Дровни везут длинный груз на короткой основе. Укладка связывает устройство саней с будущим запасом тепла для дома.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему поленья не просто сваливают у стены?</t>
+          <t xml:space="preserve">Поленья складывают в поленницу, а не только собирают в кучу. Порядок укладки превращает множество отдельных кусков дерева в устроенный запас.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда устье печи закрывают?</t>
+          <t xml:space="preserve">Печной заслон закрывает устье большого очага. Небольшая съёмная деталь имеет своё место в устройстве, вокруг которого организован домашний труд.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему Юрьев день стал поговоркой?</t>
+          <t xml:space="preserve">Юрьев день остался в известной поговорке. Народное выражение хранит след исторической перемены, который требует отдельного объяснения событий.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что можно узнать о быте по углублению в стенке?</t>
+          <t xml:space="preserve">В стенке печи устроены маленькие ниши-печурки. Небольшая деталь показывает, как домашний быт использует пространство рядом с большим очагом.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как получить ещё одно место в небольшой избе?</t>
+          <t xml:space="preserve">Полати добавляют верхний ярус в небольшую избу. Домашнее пространство растёт по высоте, когда привычной площади пола недостаточно.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему кухонные вещи собраны в одном месте?</t>
+          <t xml:space="preserve">Бабий кут собирает предметы кухонной работы рядом. Часть комнаты организована последовательностью дел, которые каждый день повторяются в доме.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли судить о человеке по одной дорогой вещи?</t>
+          <t xml:space="preserve">Дорогая шуба на снимке видна сразу, жизнь её владельца — нет. Материал одежды даёт наблюдение, но достаток требует сведений о самом человеке.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие вещи хозяин держал отдельно от повседневных?</t>
+          <t xml:space="preserve">Шкатулка отделяет личные вещи от повседневного имущества. Внутренние отделения сохраняют порядок хранения, а подлинная опись возвращает содержимому имена.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как изображение и подпись работают вместе?</t>
+          <t xml:space="preserve">Лубок соединяет изображение с подписью. Рассказ разворачивается между видимым эпизодом и прочитанной строкой — взгляд и слово работают вместе.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда текст звучит для всей комнаты?</t>
+          <t xml:space="preserve">Одну книгу читают вслух нескольким людям. Домашний текст становится общей встречей: слушатели разделяют время и голос читающего.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рассказчики не повторяют текст слово в слово?</t>
+          <t xml:space="preserve">Одна сказка живёт в разных записях. Рассказчики сохраняют узнаваемые события, но меняют слова и детали — устная традиция не повторяет страницу механически.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли назвать предмет, если о нём говорят обходно?</t>
+          <t xml:space="preserve">Загадка описывает знакомую вещь обходным путём. Образное сравнение скрывает предмет и одновременно даёт признаки, по которым его можно узнать.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем зимний Никола отличается от вешнего в народном быту?</t>
+          <t xml:space="preserve">Никола зимний и вешний входят в разные сезоны быта. Память об одном святом соединяется с разными хозяйственными обстоятельствами года.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему пословица понятна не в каждом случае?</t>
+          <t xml:space="preserve">Пословица раскрывается в подходящей жизненной ситуации. Короткая фраза переносит опыт, но её смысл нельзя одинаково приложить к любому случаю.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как отличают людей с одинаковыми именами?</t>
+          <t xml:space="preserve">Домашнее прозвище различает людей с одинаковыми именами. Внутри сообщества имя получает дополнительную семейную историю и местный смысл.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как праздничный репертуар отличается от лирического?</t>
+          <t xml:space="preserve">Зимний репертуар Лопатней продолжает годовой круг села. Назначение песни слышно через её связь с конкретным праздником и исполнением.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как записать умение, которое раньше показывали руками?</t>
+          <t xml:space="preserve">В семейном рецепте мера может быть записана «на глаз». Тетрадь сохраняет слова, а комментарий владельца помогает понять переданное руками умение.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли починить вещь, повторив её структуру?</t>
+          <t xml:space="preserve">Штопка восстанавливает переплетение внутри отверстия. Ремонт повторяет устройство ткани — повреждённая вещь получает ещё время службы.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что о дарителе рассказывает собственноручная отделка?</t>
+          <t xml:space="preserve">Собственноручная упаковка показывает заботу до открытия подарка. Внешняя отделка становится частью личного обращения к тому, кому предназначена вещь.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как простое повторение превращается в украшение комнаты?</t>
+          <t xml:space="preserve">Бумажная гирлянда растёт из повторённых элементов. Простая ручная работа собирает семью вокруг подготовки общего праздничного пространства.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем длинное украшение отличается от отдельной игрушки?</t>
+          <t xml:space="preserve">Стеклянные бусы проходят линией по нескольким веткам. Длинное украшение связывает части ёлки в общий рисунок, которого не даёт одна игрушка.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ребёнок превращается в персонажа?</t>
+          <t xml:space="preserve">Новогодняя маска помогает ребёнку войти в роль. Домашний праздник получает персонажа благодаря небольшой вещи, меняющей узнаваемое лицо.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что можно сшить из доступных домашних материалов?</t>
+          <t xml:space="preserve">Костюм для утренника собирают из доступных материалов. За детским праздничным образом остаётся семейная работа выбора, кроя и отделки.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как мастер сохраняет навык, меняя назначение изделия?</t>
+          <t xml:space="preserve">Современный мастер меняет назначение вещи и сохраняет старый приём. Традиция продолжается через освоенное действие, которому находится новая работа.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие предметы расскажут о прожитом годе без длинной хроники?</t>
+          <t xml:space="preserve">Двенадцать вещей складываются в личный рассказ о годе. Выбранные истории соединяют сезоны, людей и труд без необходимости пересказывать всё подряд.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
